--- a/projects/banr-takeout/banr_takeout_analysis.xlsx
+++ b/projects/banr-takeout/banr_takeout_analysis.xlsx
@@ -16,18 +16,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>BANR — Strategic Takeout Analysis</t>
   </si>
   <si>
-    <t>Applied recent community-bank M&amp;A multiples to BANR's TBV.</t>
+    <t>Applied community-bank M&amp;A multiples (industry ranges, not specific deals) to BANR's TBV. Market data as of April 23, 2026.</t>
   </si>
   <si>
     <t>Current Valuation Inputs</t>
   </si>
   <si>
-    <t>Current Share Price</t>
+    <t>Share Price (April 23, 2026)</t>
   </si>
   <si>
     <t>Market Cap</t>
@@ -81,7 +81,7 @@
     <t>BANR — Potential Strategic Acquirer Shortlist</t>
   </si>
   <si>
-    <t>Western-US regional banks with scale and M&amp;A history sufficient to absorb BANR ($16.4B assets).</t>
+    <t>Western-US regional banks with scale and M&amp;A history sufficient to absorb BANR ($16.4B assets). Illustrative only; no actual or reported interest.</t>
   </si>
   <si>
     <t>Ticker</t>
@@ -108,7 +108,7 @@
     <t>Zions Bancorporation</t>
   </si>
   <si>
-    <t>Western-US regional bank, $88B assets; has done large acquisitions historically; BANR's PNW franchise would strengthen Zions' relative geographic weakness in OR/WA.</t>
+    <t>Western-US regional bank, $89B assets; has done large acquisitions historically; BANR's PNW franchise would strengthen Zions' relative geographic weakness in OR/WA.</t>
   </si>
   <si>
     <t>FIBK</t>
@@ -117,7 +117,7 @@
     <t>First Interstate Bank</t>
   </si>
   <si>
-    <t>$30B-asset western regional; recent deal history (Great Western acquisition); similar community-banking culture makes integration risk lower.</t>
+    <t>$27B-asset western regional; recent deal history (Great Western acquisition); similar community-banking culture makes integration risk lower.</t>
   </si>
   <si>
     <t>WAFD</t>
@@ -126,7 +126,7 @@
     <t>WaFd Bank (Washington Federal)</t>
   </si>
   <si>
-    <t>Seattle-based $23B-asset thrift converting to commercial-banking focus; recent Luther Burbank acquisition shows M&amp;A capability; adjacent geography.</t>
+    <t>Washington-based $27B-asset bank shifting toward commercial banking; recent Luther Burbank acquisition shows M&amp;A capability; adjacent geography.</t>
   </si>
   <si>
     <t>USB</t>
@@ -135,7 +135,7 @@
     <t>U.S. Bancorp</t>
   </si>
   <si>
-    <t>Long-shot option: $685B-asset superregional; MUFG Union Bank deal showed willingness to buy PNW presence; would need regulatory concentration clearance.</t>
+    <t>Long-shot option: superregional; MUFG Union Bank deal showed willingness to buy West Coast presence; would need regulatory concentration clearance.</t>
   </si>
   <si>
     <t>Methodology &amp; Key Caveats</t>
@@ -147,10 +147,10 @@
     <t>the franchise (deposits, customer relationships, branch network) on top</t>
   </si>
   <si>
-    <t>of a bank's tangible book value. Goodwill is excluded because an acquirer</t>
-  </si>
-  <si>
-    <t>cannot use it to generate future earnings.</t>
+    <t>of a bank's tangible book value. Goodwill is excluded because it is not</t>
+  </si>
+  <si>
+    <t>tangible capital.</t>
   </si>
   <si>
     <t>Multiple ranges applied:</t>
@@ -168,18 +168,27 @@
     <t xml:space="preserve">  Strategic (1.80x):   Competitive bidding, scarce franchise, revenue synergies credited</t>
   </si>
   <si>
-    <t>These ranges reflect published reporting on recent community-bank M&amp;A</t>
-  </si>
-  <si>
-    <t>(S&amp;P Global Market Intelligence, Bank Director annual M&amp;A surveys).</t>
-  </si>
-  <si>
-    <t>Actual deal multiples vary materially by deal size, geography, regulatory</t>
+    <t>These are assumed industry ranges for community-bank M&amp;A, not multiples</t>
+  </si>
+  <si>
+    <t>taken from specific comparable deals or a specific report. Actual deal</t>
+  </si>
+  <si>
+    <t>multiples vary materially by deal size, geography, regulatory</t>
   </si>
   <si>
     <t>environment, and target-specific franchise quality.</t>
   </si>
   <si>
+    <t>Tangible book value = fiscal 2025 10-K stockholders' equity less goodwill.</t>
+  </si>
+  <si>
+    <t>Banner's other intangibles ($1.5M at Dec 31, 2025) were not deducted; the</t>
+  </si>
+  <si>
+    <t>effect is about $0.04 per share.</t>
+  </si>
+  <si>
     <t>Caveats:</t>
   </si>
   <si>
@@ -210,10 +219,10 @@
     <t xml:space="preserve">  - Fundamentals:     SEC EDGAR XBRL companyfacts API</t>
   </si>
   <si>
-    <t xml:space="preserve">  - Market data:      Yahoo Finance via yfinance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Multiple ranges:  Published industry reporting (cited above)</t>
+    <t xml:space="preserve">  - Market data:      Yahoo Finance via yfinance (as of April 23, 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - Multiple ranges:  Assumed industry ranges (not specific deals)</t>
   </si>
 </sst>
 </file>
@@ -922,7 +931,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110.7109375" customWidth="1"/>
@@ -1013,28 +1022,28 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>57</v>
-      </c>
-    </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1053,9 +1062,24 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
